--- a/public/assets/backend/docs/plantilla_import_dni.xlsx
+++ b/public/assets/backend/docs/plantilla_import_dni.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>DNI</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>ID_REGION</t>
+  </si>
+  <si>
+    <t>APELLIDO</t>
   </si>
 </sst>
 </file>
@@ -479,7 +482,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -493,7 +496,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>

--- a/public/assets/backend/docs/plantilla_import_dni.xlsx
+++ b/public/assets/backend/docs/plantilla_import_dni.xlsx
@@ -11,24 +11,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ID_REGION</t>
   </si>
   <si>
     <t>DNI</t>
   </si>
+  <si>
+    <t>NOMBRES</t>
+  </si>
+  <si>
+    <t>APELLIDOS</t>
+  </si>
+  <si>
+    <t>AGENTE</t>
+  </si>
+  <si>
+    <t>DIRECCION</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>LOCALIDAD</t>
+  </si>
+  <si>
+    <t>PROVINCIA</t>
+  </si>
+  <si>
+    <t>FECHA_INGRESO</t>
+  </si>
+  <si>
+    <t>TIPO_USUARIO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -44,11 +72,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -71,8 +105,8 @@
     <col customWidth="1" min="1" max="3" width="10.56"/>
     <col customWidth="1" min="4" max="4" width="12.67"/>
     <col customWidth="1" min="5" max="5" width="10.56"/>
-    <col customWidth="1" min="6" max="7" width="12.67"/>
-    <col customWidth="1" min="8" max="26" width="10.56"/>
+    <col customWidth="1" min="6" max="6" width="12.67"/>
+    <col customWidth="1" min="10" max="10" width="13.56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -82,7 +116,33 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
